--- a/data/Framework_1_Belgique.xlsx
+++ b/data/Framework_1_Belgique.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://digiplace-my.sharepoint.com/personal/aurelien_brun_wavestone_com/Documents/Desktop/mapper/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="255" documentId="8_{6DCC9DED-70CC-49C8-8D15-2391C499D3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91C29AFD-2F16-404C-979B-22F2C7CB81B8}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="8_{6DCC9DED-70CC-49C8-8D15-2391C499D3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B36ECE3-3F66-4F07-9468-2FA889A36BC3}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B5DE09A6-CED4-42BE-9EC0-2641ED5338CA}"/>
+    <workbookView minimized="1" xWindow="4850" yWindow="4510" windowWidth="5610" windowHeight="3200" xr2:uid="{B5DE09A6-CED4-42BE-9EC0-2641ED5338CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Belgique Cyfun 2025" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="681">
   <si>
     <t>DE.CM-01.1</t>
   </si>
@@ -2076,13 +2076,19 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>Important</t>
+  </si>
+  <si>
+    <t>Essential</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2116,6 +2122,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2125,11 +2137,20 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -2141,13 +2162,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2168,6 +2195,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2393,15 +2424,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F10B81A-1735-44BB-81AD-BFF6EA44DA32}">
-  <dimension ref="A1:D929"/>
+  <dimension ref="A1:F929"/>
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="2"/>
     <col min="2" max="2" width="31.25" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="10.6640625" style="2"/>
+    <col min="3" max="4" width="10.6640625" style="2"/>
+    <col min="7" max="16384" width="10.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6" ht="15" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>458</v>
       </c>
@@ -2414,8 +2446,14 @@
       <c r="D1" s="1" t="s">
         <v>677</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>459</v>
       </c>
@@ -2428,8 +2466,14 @@
       <c r="D2" s="1" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>460</v>
       </c>
@@ -2442,8 +2486,14 @@
       <c r="D3" s="1" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>461</v>
       </c>
@@ -2456,8 +2506,14 @@
       <c r="D4" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>462</v>
       </c>
@@ -2470,8 +2526,14 @@
       <c r="D5" s="1" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>463</v>
       </c>
@@ -2484,8 +2546,14 @@
       <c r="D6" s="1" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>464</v>
       </c>
@@ -2498,8 +2566,14 @@
       <c r="D7" s="1" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>465</v>
       </c>
@@ -2512,8 +2586,14 @@
       <c r="D8" s="1" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>466</v>
       </c>
@@ -2526,8 +2606,14 @@
       <c r="D9" s="1" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>467</v>
       </c>
@@ -2540,8 +2626,14 @@
       <c r="D10" s="1" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>468</v>
       </c>
@@ -2554,8 +2646,14 @@
       <c r="D11" s="1" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="2" t="s">
         <v>469</v>
       </c>
@@ -2568,8 +2666,14 @@
       <c r="D12" s="1" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>470</v>
       </c>
@@ -2582,8 +2686,14 @@
       <c r="D13" s="1" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
         <v>471</v>
       </c>
@@ -2596,8 +2706,14 @@
       <c r="D14" s="1" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="2" t="s">
         <v>472</v>
       </c>
@@ -2610,8 +2726,14 @@
       <c r="D15" s="1" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
         <v>473</v>
       </c>
@@ -2624,8 +2746,14 @@
       <c r="D16" s="1" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>474</v>
       </c>
@@ -2638,8 +2766,14 @@
       <c r="D17" s="1" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
         <v>475</v>
       </c>
@@ -2652,8 +2786,14 @@
       <c r="D18" s="1" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
         <v>476</v>
       </c>
@@ -2666,8 +2806,14 @@
       <c r="D19" s="1" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="2" t="s">
         <v>477</v>
       </c>
@@ -2680,8 +2826,14 @@
       <c r="D20" s="1" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="2" t="s">
         <v>478</v>
       </c>
@@ -2694,8 +2846,14 @@
       <c r="D21" s="1" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="2" t="s">
         <v>479</v>
       </c>
@@ -2708,8 +2866,14 @@
       <c r="D22" s="1" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="2" t="s">
         <v>480</v>
       </c>
@@ -2722,8 +2886,14 @@
       <c r="D23" s="1" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
         <v>481</v>
       </c>
@@ -2736,8 +2906,14 @@
       <c r="D24" s="1" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
         <v>482</v>
       </c>
@@ -2750,8 +2926,14 @@
       <c r="D25" s="1" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
         <v>483</v>
       </c>
@@ -2764,8 +2946,14 @@
       <c r="D26" s="1" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="E26" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
         <v>484</v>
       </c>
@@ -2778,8 +2966,14 @@
       <c r="D27" s="1" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
         <v>485</v>
       </c>
@@ -2792,8 +2986,14 @@
       <c r="D28" s="1" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
         <v>486</v>
       </c>
@@ -2806,8 +3006,14 @@
       <c r="D29" s="1" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
         <v>487</v>
       </c>
@@ -2820,8 +3026,14 @@
       <c r="D30" s="1" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="2" t="s">
         <v>488</v>
       </c>
@@ -2834,8 +3046,14 @@
       <c r="D31" s="1" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
         <v>489</v>
       </c>
@@ -2848,8 +3066,14 @@
       <c r="D32" s="1" t="s">
         <v>367</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="2" t="s">
         <v>490</v>
       </c>
@@ -2862,8 +3086,14 @@
       <c r="D33" s="1" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="2" t="s">
         <v>491</v>
       </c>
@@ -2876,8 +3106,14 @@
       <c r="D34" s="1" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="E34" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="2" t="s">
         <v>492</v>
       </c>
@@ -2890,8 +3126,14 @@
       <c r="D35" s="1" t="s">
         <v>373</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="2" t="s">
         <v>493</v>
       </c>
@@ -2904,8 +3146,14 @@
       <c r="D36" s="1" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="2" t="s">
         <v>494</v>
       </c>
@@ -2918,8 +3166,14 @@
       <c r="D37" s="1" t="s">
         <v>377</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
         <v>495</v>
       </c>
@@ -2932,8 +3186,14 @@
       <c r="D38" s="1" t="s">
         <v>379</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="2" t="s">
         <v>496</v>
       </c>
@@ -2946,8 +3206,14 @@
       <c r="D39" s="1" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="2" t="s">
         <v>497</v>
       </c>
@@ -2960,8 +3226,14 @@
       <c r="D40" s="1" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="E40" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
         <v>498</v>
       </c>
@@ -2974,8 +3246,14 @@
       <c r="D41" s="1" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="E41" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="2" t="s">
         <v>499</v>
       </c>
@@ -2988,8 +3266,14 @@
       <c r="D42" s="1" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="E42" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" s="2" t="s">
         <v>500</v>
       </c>
@@ -3002,8 +3286,14 @@
       <c r="D43" s="1" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="E43" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
         <v>501</v>
       </c>
@@ -3016,8 +3306,14 @@
       <c r="D44" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="E44" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" s="2" t="s">
         <v>502</v>
       </c>
@@ -3030,8 +3326,14 @@
       <c r="D45" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
+      <c r="E45" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
         <v>503</v>
       </c>
@@ -3044,8 +3346,14 @@
       <c r="D46" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="E46" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="2" t="s">
         <v>504</v>
       </c>
@@ -3058,8 +3366,14 @@
       <c r="D47" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="E47" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="2" t="s">
         <v>505</v>
       </c>
@@ -3072,8 +3386,14 @@
       <c r="D48" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
+      <c r="E48" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="2" t="s">
         <v>506</v>
       </c>
@@ -3086,8 +3406,14 @@
       <c r="D49" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="50" spans="1:4">
+      <c r="E49" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="2" t="s">
         <v>507</v>
       </c>
@@ -3100,8 +3426,14 @@
       <c r="D50" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
+      <c r="E50" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
         <v>508</v>
       </c>
@@ -3114,8 +3446,14 @@
       <c r="D51" s="1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="E51" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="2" t="s">
         <v>509</v>
       </c>
@@ -3128,8 +3466,14 @@
       <c r="D52" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="53" spans="1:4">
+      <c r="E52" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="2" t="s">
         <v>510</v>
       </c>
@@ -3142,8 +3486,14 @@
       <c r="D53" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="E53" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="2" t="s">
         <v>511</v>
       </c>
@@ -3156,8 +3506,14 @@
       <c r="D54" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="E54" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="2" t="s">
         <v>512</v>
       </c>
@@ -3170,8 +3526,14 @@
       <c r="D55" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="56" spans="1:4">
+      <c r="E55" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" s="2" t="s">
         <v>513</v>
       </c>
@@ -3184,8 +3546,14 @@
       <c r="D56" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="57" spans="1:4">
+      <c r="E56" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" s="2" t="s">
         <v>514</v>
       </c>
@@ -3198,8 +3566,14 @@
       <c r="D57" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="58" spans="1:4">
+      <c r="E57" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" s="2" t="s">
         <v>515</v>
       </c>
@@ -3212,8 +3586,14 @@
       <c r="D58" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="59" spans="1:4">
+      <c r="E58" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" s="2" t="s">
         <v>516</v>
       </c>
@@ -3226,8 +3606,14 @@
       <c r="D59" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="E59" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" s="2" t="s">
         <v>517</v>
       </c>
@@ -3240,8 +3626,14 @@
       <c r="D60" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
+      <c r="E60" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
         <v>518</v>
       </c>
@@ -3254,8 +3646,14 @@
       <c r="D61" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="E61" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="2" t="s">
         <v>519</v>
       </c>
@@ -3268,8 +3666,14 @@
       <c r="D62" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="E62" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" s="2" t="s">
         <v>520</v>
       </c>
@@ -3282,8 +3686,14 @@
       <c r="D63" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="E63" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" s="2" t="s">
         <v>521</v>
       </c>
@@ -3296,8 +3706,14 @@
       <c r="D64" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="65" spans="1:4">
+      <c r="E64" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" s="2" t="s">
         <v>522</v>
       </c>
@@ -3310,8 +3726,14 @@
       <c r="D65" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="E65" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" s="2" t="s">
         <v>523</v>
       </c>
@@ -3324,8 +3746,14 @@
       <c r="D66" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="E66" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
         <v>524</v>
       </c>
@@ -3338,8 +3766,14 @@
       <c r="D67" s="1" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="68" spans="1:4">
+      <c r="E67" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" s="2" t="s">
         <v>525</v>
       </c>
@@ -3352,8 +3786,14 @@
       <c r="D68" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="69" spans="1:4">
+      <c r="E68" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" s="2" t="s">
         <v>526</v>
       </c>
@@ -3366,8 +3806,14 @@
       <c r="D69" s="1" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="70" spans="1:4">
+      <c r="E69" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F69" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" s="2" t="s">
         <v>527</v>
       </c>
@@ -3380,8 +3826,14 @@
       <c r="D70" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="E70" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="2" t="s">
         <v>528</v>
       </c>
@@ -3394,8 +3846,14 @@
       <c r="D71" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
+      <c r="E71" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F71" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="2" t="s">
         <v>529</v>
       </c>
@@ -3408,8 +3866,14 @@
       <c r="D72" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="73" spans="1:4">
+      <c r="E72" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" s="2" t="s">
         <v>530</v>
       </c>
@@ -3422,8 +3886,14 @@
       <c r="D73" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="E73" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="2" t="s">
         <v>531</v>
       </c>
@@ -3436,8 +3906,14 @@
       <c r="D74" s="1" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="75" spans="1:4">
+      <c r="E74" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" s="2" t="s">
         <v>532</v>
       </c>
@@ -3450,8 +3926,14 @@
       <c r="D75" s="1" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="76" spans="1:4">
+      <c r="E75" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" s="2" t="s">
         <v>533</v>
       </c>
@@ -3464,8 +3946,14 @@
       <c r="D76" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="77" spans="1:4">
+      <c r="E76" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" s="2" t="s">
         <v>534</v>
       </c>
@@ -3478,8 +3966,14 @@
       <c r="D77" s="1" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="78" spans="1:4">
+      <c r="E77" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="2" t="s">
         <v>535</v>
       </c>
@@ -3492,8 +3986,14 @@
       <c r="D78" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="79" spans="1:4">
+      <c r="E78" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" s="2" t="s">
         <v>536</v>
       </c>
@@ -3506,8 +4006,14 @@
       <c r="D79" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="80" spans="1:4">
+      <c r="E79" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F79" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" s="2" t="s">
         <v>537</v>
       </c>
@@ -3520,8 +4026,14 @@
       <c r="D80" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="81" spans="1:4">
+      <c r="E80" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" s="2" t="s">
         <v>538</v>
       </c>
@@ -3534,8 +4046,14 @@
       <c r="D81" s="1" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="E81" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F81" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" s="2" t="s">
         <v>539</v>
       </c>
@@ -3548,8 +4066,14 @@
       <c r="D82" s="1" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="83" spans="1:4">
+      <c r="E82" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" s="2" t="s">
         <v>540</v>
       </c>
@@ -3562,8 +4086,14 @@
       <c r="D83" s="1" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="84" spans="1:4">
+      <c r="E83" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" s="2" t="s">
         <v>541</v>
       </c>
@@ -3576,8 +4106,14 @@
       <c r="D84" s="1" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="85" spans="1:4">
+      <c r="E84" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" s="2" t="s">
         <v>542</v>
       </c>
@@ -3590,8 +4126,14 @@
       <c r="D85" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="86" spans="1:4">
+      <c r="E85" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" s="2" t="s">
         <v>543</v>
       </c>
@@ -3604,8 +4146,14 @@
       <c r="D86" s="1" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="87" spans="1:4">
+      <c r="E86" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" s="2" t="s">
         <v>544</v>
       </c>
@@ -3618,8 +4166,14 @@
       <c r="D87" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="88" spans="1:4">
+      <c r="E87" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F87" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" s="2" t="s">
         <v>545</v>
       </c>
@@ -3632,8 +4186,14 @@
       <c r="D88" s="1" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="89" spans="1:4">
+      <c r="E88" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F88" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" s="2" t="s">
         <v>546</v>
       </c>
@@ -3646,8 +4206,14 @@
       <c r="D89" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:4">
+      <c r="E89" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" s="2" t="s">
         <v>547</v>
       </c>
@@ -3660,8 +4226,14 @@
       <c r="D90" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="91" spans="1:4">
+      <c r="E90" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F90" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" s="2" t="s">
         <v>548</v>
       </c>
@@ -3674,8 +4246,14 @@
       <c r="D91" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="92" spans="1:4">
+      <c r="E91" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F91" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" s="2" t="s">
         <v>549</v>
       </c>
@@ -3688,8 +4266,14 @@
       <c r="D92" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="93" spans="1:4">
+      <c r="E92" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" s="2" t="s">
         <v>550</v>
       </c>
@@ -3702,8 +4286,14 @@
       <c r="D93" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="94" spans="1:4">
+      <c r="E93" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F93" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" s="2" t="s">
         <v>551</v>
       </c>
@@ -3716,8 +4306,14 @@
       <c r="D94" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="95" spans="1:4">
+      <c r="E94" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F94" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" s="2" t="s">
         <v>552</v>
       </c>
@@ -3730,8 +4326,14 @@
       <c r="D95" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="96" spans="1:4">
+      <c r="E95" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" s="2" t="s">
         <v>553</v>
       </c>
@@ -3744,8 +4346,14 @@
       <c r="D96" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="97" spans="1:4">
+      <c r="E96" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F96" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="2" t="s">
         <v>554</v>
       </c>
@@ -3758,8 +4366,14 @@
       <c r="D97" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="98" spans="1:4">
+      <c r="E97" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F97" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="2" t="s">
         <v>555</v>
       </c>
@@ -3772,8 +4386,14 @@
       <c r="D98" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="99" spans="1:4">
+      <c r="E98" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F98" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="2" t="s">
         <v>556</v>
       </c>
@@ -3786,8 +4406,14 @@
       <c r="D99" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="100" spans="1:4">
+      <c r="E99" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F99" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" s="2" t="s">
         <v>557</v>
       </c>
@@ -3800,8 +4426,14 @@
       <c r="D100" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="101" spans="1:4">
+      <c r="E100" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F100" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" s="2" t="s">
         <v>558</v>
       </c>
@@ -3814,8 +4446,14 @@
       <c r="D101" s="1" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="102" spans="1:4">
+      <c r="E101" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F101" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" s="2" t="s">
         <v>559</v>
       </c>
@@ -3828,8 +4466,14 @@
       <c r="D102" s="1" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
+      <c r="E102" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F102" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" s="2" t="s">
         <v>560</v>
       </c>
@@ -3842,8 +4486,14 @@
       <c r="D103" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="104" spans="1:4">
+      <c r="E103" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F103" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" s="2" t="s">
         <v>561</v>
       </c>
@@ -3856,8 +4506,14 @@
       <c r="D104" s="1" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
+      <c r="E104" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F104" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" s="2" t="s">
         <v>562</v>
       </c>
@@ -3870,8 +4526,14 @@
       <c r="D105" s="1" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="106" spans="1:4">
+      <c r="E105" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F105" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" s="2" t="s">
         <v>563</v>
       </c>
@@ -3884,8 +4546,14 @@
       <c r="D106" s="1" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="107" spans="1:4">
+      <c r="E106" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F106" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" s="2" t="s">
         <v>564</v>
       </c>
@@ -3898,8 +4566,14 @@
       <c r="D107" s="1" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
+      <c r="E107" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F107" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="2" t="s">
         <v>565</v>
       </c>
@@ -3912,8 +4586,14 @@
       <c r="D108" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="109" spans="1:4">
+      <c r="E108" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F108" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="2" t="s">
         <v>566</v>
       </c>
@@ -3926,8 +4606,14 @@
       <c r="D109" s="1" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
+      <c r="E109" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" s="2" t="s">
         <v>567</v>
       </c>
@@ -3940,8 +4626,14 @@
       <c r="D110" s="1" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="111" spans="1:4">
+      <c r="E110" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F110" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" s="2" t="s">
         <v>568</v>
       </c>
@@ -3954,8 +4646,14 @@
       <c r="D111" s="1" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
+      <c r="E111" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F111" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" s="2" t="s">
         <v>569</v>
       </c>
@@ -3968,8 +4666,14 @@
       <c r="D112" s="1" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="113" spans="1:4">
+      <c r="E112" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F112" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" s="2" t="s">
         <v>570</v>
       </c>
@@ -3982,8 +4686,14 @@
       <c r="D113" s="1" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="114" spans="1:4">
+      <c r="E113" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F113" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" s="2" t="s">
         <v>571</v>
       </c>
@@ -3996,8 +4706,14 @@
       <c r="D114" s="1" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="115" spans="1:4">
+      <c r="E114" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F114" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="2" t="s">
         <v>572</v>
       </c>
@@ -4010,8 +4726,14 @@
       <c r="D115" s="1" t="s">
         <v>425</v>
       </c>
-    </row>
-    <row r="116" spans="1:4">
+      <c r="E115" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" s="2" t="s">
         <v>573</v>
       </c>
@@ -4024,8 +4746,14 @@
       <c r="D116" s="1" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="117" spans="1:4">
+      <c r="E116" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F116" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" s="2" t="s">
         <v>574</v>
       </c>
@@ -4038,8 +4766,14 @@
       <c r="D117" s="1" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="118" spans="1:4">
+      <c r="E117" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F117" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" s="2" t="s">
         <v>575</v>
       </c>
@@ -4052,8 +4786,14 @@
       <c r="D118" s="1" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="119" spans="1:4">
+      <c r="E118" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F118" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" s="2" t="s">
         <v>576</v>
       </c>
@@ -4066,8 +4806,14 @@
       <c r="D119" s="1" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="120" spans="1:4">
+      <c r="E119" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F119" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" s="2" t="s">
         <v>577</v>
       </c>
@@ -4080,8 +4826,14 @@
       <c r="D120" s="1" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="121" spans="1:4">
+      <c r="E120" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F120" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" s="2" t="s">
         <v>578</v>
       </c>
@@ -4094,8 +4846,14 @@
       <c r="D121" s="1" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="122" spans="1:4">
+      <c r="E121" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F121" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" s="2" t="s">
         <v>579</v>
       </c>
@@ -4108,8 +4866,14 @@
       <c r="D122" s="1" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="123" spans="1:4">
+      <c r="E122" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F122" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" s="2" t="s">
         <v>580</v>
       </c>
@@ -4122,8 +4886,14 @@
       <c r="D123" s="1" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="124" spans="1:4">
+      <c r="E123" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F123" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" s="2" t="s">
         <v>581</v>
       </c>
@@ -4136,8 +4906,14 @@
       <c r="D124" s="1" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="125" spans="1:4">
+      <c r="E124" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F124" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" s="2" t="s">
         <v>582</v>
       </c>
@@ -4150,8 +4926,14 @@
       <c r="D125" s="1" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="126" spans="1:4">
+      <c r="E125" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F125" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" s="2" t="s">
         <v>583</v>
       </c>
@@ -4164,8 +4946,14 @@
       <c r="D126" s="1" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="127" spans="1:4">
+      <c r="E126" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" s="2" t="s">
         <v>584</v>
       </c>
@@ -4178,8 +4966,14 @@
       <c r="D127" s="1" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="128" spans="1:4">
+      <c r="E127" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F127" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" s="2" t="s">
         <v>585</v>
       </c>
@@ -4192,8 +4986,14 @@
       <c r="D128" s="1" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="129" spans="1:4">
+      <c r="E128" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F128" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" s="2" t="s">
         <v>586</v>
       </c>
@@ -4206,8 +5006,14 @@
       <c r="D129" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="130" spans="1:4">
+      <c r="E129" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F129" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" s="2" t="s">
         <v>587</v>
       </c>
@@ -4220,8 +5026,14 @@
       <c r="D130" s="1" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="131" spans="1:4">
+      <c r="E130" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F130" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" s="2" t="s">
         <v>588</v>
       </c>
@@ -4234,8 +5046,14 @@
       <c r="D131" s="1" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="132" spans="1:4">
+      <c r="E131" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F131" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" s="2" t="s">
         <v>589</v>
       </c>
@@ -4248,8 +5066,14 @@
       <c r="D132" s="1" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="133" spans="1:4">
+      <c r="E132" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F132" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" s="2" t="s">
         <v>590</v>
       </c>
@@ -4262,8 +5086,14 @@
       <c r="D133" s="1" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="134" spans="1:4">
+      <c r="E133" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F133" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" s="2" t="s">
         <v>591</v>
       </c>
@@ -4276,8 +5106,14 @@
       <c r="D134" s="1" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="135" spans="1:4">
+      <c r="E134" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F134" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" s="2" t="s">
         <v>592</v>
       </c>
@@ -4290,8 +5126,14 @@
       <c r="D135" s="1" t="s">
         <v>405</v>
       </c>
-    </row>
-    <row r="136" spans="1:4">
+      <c r="E135" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F135" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" s="2" t="s">
         <v>593</v>
       </c>
@@ -4304,8 +5146,14 @@
       <c r="D136" s="1" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="137" spans="1:4">
+      <c r="E136" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F136" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="A137" s="2" t="s">
         <v>594</v>
       </c>
@@ -4318,8 +5166,14 @@
       <c r="D137" s="1" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="138" spans="1:4">
+      <c r="E137" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F137" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138" s="2" t="s">
         <v>595</v>
       </c>
@@ -4332,8 +5186,14 @@
       <c r="D138" s="1" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="139" spans="1:4">
+      <c r="E138" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F138" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" s="2" t="s">
         <v>596</v>
       </c>
@@ -4346,8 +5206,14 @@
       <c r="D139" s="1" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="140" spans="1:4">
+      <c r="E139" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F139" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" s="2" t="s">
         <v>597</v>
       </c>
@@ -4360,8 +5226,14 @@
       <c r="D140" s="1" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="141" spans="1:4">
+      <c r="E140" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F140" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141" s="2" t="s">
         <v>598</v>
       </c>
@@ -4374,8 +5246,14 @@
       <c r="D141" s="1" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="142" spans="1:4">
+      <c r="E141" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F141" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" s="2" t="s">
         <v>599</v>
       </c>
@@ -4388,8 +5266,14 @@
       <c r="D142" s="1" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="143" spans="1:4">
+      <c r="E142" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F142" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" s="2" t="s">
         <v>600</v>
       </c>
@@ -4402,8 +5286,14 @@
       <c r="D143" s="1" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="144" spans="1:4">
+      <c r="E143" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F143" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" s="2" t="s">
         <v>601</v>
       </c>
@@ -4416,8 +5306,14 @@
       <c r="D144" s="1" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="145" spans="1:4">
+      <c r="E144" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F144" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" s="2" t="s">
         <v>602</v>
       </c>
@@ -4430,8 +5326,14 @@
       <c r="D145" s="1" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="146" spans="1:4">
+      <c r="E145" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F145" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" s="2" t="s">
         <v>603</v>
       </c>
@@ -4444,8 +5346,14 @@
       <c r="D146" s="1" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="147" spans="1:4">
+      <c r="E146" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F146" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" s="2" t="s">
         <v>604</v>
       </c>
@@ -4458,8 +5366,14 @@
       <c r="D147" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="148" spans="1:4">
+      <c r="E147" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F147" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" s="2" t="s">
         <v>605</v>
       </c>
@@ -4472,8 +5386,14 @@
       <c r="D148" s="1" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="149" spans="1:4">
+      <c r="E148" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F148" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" s="2" t="s">
         <v>606</v>
       </c>
@@ -4486,8 +5406,14 @@
       <c r="D149" s="1" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="150" spans="1:4">
+      <c r="E149" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F149" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" s="2" t="s">
         <v>607</v>
       </c>
@@ -4500,8 +5426,14 @@
       <c r="D150" s="1" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="151" spans="1:4">
+      <c r="E150" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F150" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" s="2" t="s">
         <v>608</v>
       </c>
@@ -4514,8 +5446,14 @@
       <c r="D151" s="1" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="152" spans="1:4">
+      <c r="E151" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F151" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" s="2" t="s">
         <v>609</v>
       </c>
@@ -4528,8 +5466,14 @@
       <c r="D152" s="1" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="153" spans="1:4">
+      <c r="E152" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F152" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153" s="2" t="s">
         <v>610</v>
       </c>
@@ -4542,8 +5486,14 @@
       <c r="D153" s="1" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="154" spans="1:4">
+      <c r="E153" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F153" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154" s="2" t="s">
         <v>611</v>
       </c>
@@ -4556,8 +5506,14 @@
       <c r="D154" s="1" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="155" spans="1:4">
+      <c r="E154" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F154" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
       <c r="A155" s="2" t="s">
         <v>612</v>
       </c>
@@ -4570,8 +5526,14 @@
       <c r="D155" s="1" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="156" spans="1:4">
+      <c r="E155" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F155" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
       <c r="A156" s="2" t="s">
         <v>613</v>
       </c>
@@ -4584,8 +5546,14 @@
       <c r="D156" s="1" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="157" spans="1:4">
+      <c r="E156" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F156" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
       <c r="A157" s="2" t="s">
         <v>614</v>
       </c>
@@ -4598,8 +5566,14 @@
       <c r="D157" s="1" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="158" spans="1:4">
+      <c r="E157" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F157" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
       <c r="A158" s="2" t="s">
         <v>615</v>
       </c>
@@ -4612,8 +5586,14 @@
       <c r="D158" s="1" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="159" spans="1:4">
+      <c r="E158" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F158" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
       <c r="A159" s="2" t="s">
         <v>616</v>
       </c>
@@ -4626,8 +5606,14 @@
       <c r="D159" s="1" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="160" spans="1:4">
+      <c r="E159" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F159" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160" s="2" t="s">
         <v>617</v>
       </c>
@@ -4640,8 +5626,14 @@
       <c r="D160" s="1" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="161" spans="1:4">
+      <c r="E160" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F160" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
       <c r="A161" s="2" t="s">
         <v>618</v>
       </c>
@@ -4654,8 +5646,14 @@
       <c r="D161" s="1" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="162" spans="1:4">
+      <c r="E161" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F161" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
       <c r="A162" s="2" t="s">
         <v>619</v>
       </c>
@@ -4668,8 +5666,14 @@
       <c r="D162" s="1" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="163" spans="1:4">
+      <c r="E162" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F162" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
       <c r="A163" s="2" t="s">
         <v>620</v>
       </c>
@@ -4682,8 +5686,14 @@
       <c r="D163" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="164" spans="1:4">
+      <c r="E163" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F163" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="A164" s="2" t="s">
         <v>621</v>
       </c>
@@ -4696,8 +5706,14 @@
       <c r="D164" s="1" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="165" spans="1:4">
+      <c r="E164" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F164" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
       <c r="A165" s="2" t="s">
         <v>622</v>
       </c>
@@ -4710,8 +5726,14 @@
       <c r="D165" s="1" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="166" spans="1:4">
+      <c r="E165" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F165" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
       <c r="A166" s="2" t="s">
         <v>623</v>
       </c>
@@ -4724,8 +5746,14 @@
       <c r="D166" s="1" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="167" spans="1:4">
+      <c r="E166" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F166" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="A167" s="2" t="s">
         <v>624</v>
       </c>
@@ -4738,8 +5766,14 @@
       <c r="D167" s="1" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="168" spans="1:4">
+      <c r="E167" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F167" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="A168" s="2" t="s">
         <v>625</v>
       </c>
@@ -4752,8 +5786,14 @@
       <c r="D168" s="1" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="169" spans="1:4">
+      <c r="E168" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F168" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
       <c r="A169" s="2" t="s">
         <v>626</v>
       </c>
@@ -4766,8 +5806,14 @@
       <c r="D169" s="1" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="170" spans="1:4">
+      <c r="E169" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F169" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
       <c r="A170" s="2" t="s">
         <v>627</v>
       </c>
@@ -4780,8 +5826,14 @@
       <c r="D170" s="1" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="171" spans="1:4">
+      <c r="E170" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F170" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
       <c r="A171" s="2" t="s">
         <v>628</v>
       </c>
@@ -4794,8 +5846,14 @@
       <c r="D171" s="1" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="172" spans="1:4">
+      <c r="E171" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F171" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
       <c r="A172" s="2" t="s">
         <v>629</v>
       </c>
@@ -4808,8 +5866,14 @@
       <c r="D172" s="1" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="173" spans="1:4">
+      <c r="E172" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F172" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
       <c r="A173" s="2" t="s">
         <v>630</v>
       </c>
@@ -4822,8 +5886,14 @@
       <c r="D173" s="1" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="174" spans="1:4">
+      <c r="E173" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F173" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
       <c r="A174" s="2" t="s">
         <v>631</v>
       </c>
@@ -4836,8 +5906,14 @@
       <c r="D174" s="1" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="175" spans="1:4">
+      <c r="E174" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F174" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
       <c r="A175" s="2" t="s">
         <v>632</v>
       </c>
@@ -4850,8 +5926,14 @@
       <c r="D175" s="1" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="176" spans="1:4">
+      <c r="E175" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F175" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
       <c r="A176" s="2" t="s">
         <v>633</v>
       </c>
@@ -4864,8 +5946,14 @@
       <c r="D176" s="1" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="177" spans="1:4">
+      <c r="E176" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F176" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
       <c r="A177" s="2" t="s">
         <v>634</v>
       </c>
@@ -4878,8 +5966,14 @@
       <c r="D177" s="1" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="178" spans="1:4">
+      <c r="E177" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F177" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
       <c r="A178" s="2" t="s">
         <v>635</v>
       </c>
@@ -4892,8 +5986,14 @@
       <c r="D178" s="1" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="179" spans="1:4">
+      <c r="E178" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F178" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
       <c r="A179" s="2" t="s">
         <v>636</v>
       </c>
@@ -4906,8 +6006,14 @@
       <c r="D179" s="1" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="180" spans="1:4">
+      <c r="E179" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F179" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
       <c r="A180" s="2" t="s">
         <v>637</v>
       </c>
@@ -4920,8 +6026,14 @@
       <c r="D180" s="1" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="181" spans="1:4">
+      <c r="E180" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F180" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
       <c r="A181" s="2" t="s">
         <v>638</v>
       </c>
@@ -4934,8 +6046,14 @@
       <c r="D181" s="1" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="182" spans="1:4">
+      <c r="E181" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F181" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
       <c r="A182" s="2" t="s">
         <v>639</v>
       </c>
@@ -4948,8 +6066,14 @@
       <c r="D182" s="1" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="183" spans="1:4">
+      <c r="E182" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F182" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
       <c r="A183" s="2" t="s">
         <v>640</v>
       </c>
@@ -4962,8 +6086,14 @@
       <c r="D183" s="1" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="184" spans="1:4">
+      <c r="E183" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F183" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
       <c r="A184" s="2" t="s">
         <v>641</v>
       </c>
@@ -4976,8 +6106,14 @@
       <c r="D184" s="1" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="185" spans="1:4">
+      <c r="E184" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F184" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
       <c r="A185" s="2" t="s">
         <v>642</v>
       </c>
@@ -4990,8 +6126,14 @@
       <c r="D185" s="1" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="186" spans="1:4">
+      <c r="E185" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F185" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
       <c r="A186" s="2" t="s">
         <v>643</v>
       </c>
@@ -5004,8 +6146,14 @@
       <c r="D186" s="1" t="s">
         <v>283</v>
       </c>
-    </row>
-    <row r="187" spans="1:4">
+      <c r="E186" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F186" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
       <c r="A187" s="2" t="s">
         <v>644</v>
       </c>
@@ -5018,8 +6166,14 @@
       <c r="D187" s="1" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="188" spans="1:4">
+      <c r="E187" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F187" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
       <c r="A188" s="2" t="s">
         <v>645</v>
       </c>
@@ -5032,8 +6186,14 @@
       <c r="D188" s="1" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="189" spans="1:4">
+      <c r="E188" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F188" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
       <c r="A189" s="2" t="s">
         <v>646</v>
       </c>
@@ -5046,8 +6206,14 @@
       <c r="D189" s="1" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="190" spans="1:4">
+      <c r="E189" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F189" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
       <c r="A190" s="2" t="s">
         <v>647</v>
       </c>
@@ -5060,8 +6226,14 @@
       <c r="D190" s="1" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="191" spans="1:4">
+      <c r="E190" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F190" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
       <c r="A191" s="2" t="s">
         <v>648</v>
       </c>
@@ -5074,8 +6246,14 @@
       <c r="D191" s="1" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="192" spans="1:4">
+      <c r="E191" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F191" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
       <c r="A192" s="2" t="s">
         <v>649</v>
       </c>
@@ -5088,8 +6266,14 @@
       <c r="D192" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="193" spans="1:4">
+      <c r="E192" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F192" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
       <c r="A193" s="2" t="s">
         <v>650</v>
       </c>
@@ -5102,8 +6286,14 @@
       <c r="D193" s="1" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="194" spans="1:4">
+      <c r="E193" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F193" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
       <c r="A194" s="2" t="s">
         <v>651</v>
       </c>
@@ -5116,8 +6306,14 @@
       <c r="D194" s="1" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="195" spans="1:4">
+      <c r="E194" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F194" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
       <c r="A195" s="2" t="s">
         <v>652</v>
       </c>
@@ -5130,8 +6326,14 @@
       <c r="D195" s="1" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="196" spans="1:4">
+      <c r="E195" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F195" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
       <c r="A196" s="2" t="s">
         <v>653</v>
       </c>
@@ -5144,8 +6346,14 @@
       <c r="D196" s="1" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="197" spans="1:4">
+      <c r="E196" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F196" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
       <c r="A197" s="2" t="s">
         <v>654</v>
       </c>
@@ -5158,8 +6366,14 @@
       <c r="D197" s="1" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="198" spans="1:4">
+      <c r="E197" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F197" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
       <c r="A198" s="2" t="s">
         <v>655</v>
       </c>
@@ -5172,8 +6386,14 @@
       <c r="D198" s="1" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="199" spans="1:4">
+      <c r="E198" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F198" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
       <c r="A199" s="2" t="s">
         <v>656</v>
       </c>
@@ -5186,8 +6406,14 @@
       <c r="D199" s="1" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="200" spans="1:4">
+      <c r="E199" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F199" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
       <c r="A200" s="2" t="s">
         <v>657</v>
       </c>
@@ -5200,8 +6426,14 @@
       <c r="D200" s="1" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="201" spans="1:4">
+      <c r="E200" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F200" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
       <c r="A201" s="2" t="s">
         <v>658</v>
       </c>
@@ -5214,8 +6446,14 @@
       <c r="D201" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="202" spans="1:4">
+      <c r="E201" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F201" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
       <c r="A202" s="2" t="s">
         <v>659</v>
       </c>
@@ -5228,8 +6466,14 @@
       <c r="D202" s="1" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="203" spans="1:4">
+      <c r="E202" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F202" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
       <c r="A203" s="2" t="s">
         <v>660</v>
       </c>
@@ -5242,8 +6486,14 @@
       <c r="D203" s="1" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="204" spans="1:4">
+      <c r="E203" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F203" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
       <c r="A204" s="2" t="s">
         <v>661</v>
       </c>
@@ -5256,8 +6506,14 @@
       <c r="D204" s="2" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="205" spans="1:4">
+      <c r="E204" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F204" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
       <c r="A205" s="2" t="s">
         <v>662</v>
       </c>
@@ -5270,8 +6526,14 @@
       <c r="D205" s="1" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="206" spans="1:4">
+      <c r="E205" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F205" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
       <c r="A206" s="2" t="s">
         <v>663</v>
       </c>
@@ -5284,8 +6546,14 @@
       <c r="D206" s="1" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="207" spans="1:4">
+      <c r="E206" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F206" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
       <c r="A207" s="2" t="s">
         <v>664</v>
       </c>
@@ -5298,8 +6566,14 @@
       <c r="D207" s="1" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="208" spans="1:4">
+      <c r="E207" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F207" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
       <c r="A208" s="2" t="s">
         <v>665</v>
       </c>
@@ -5312,8 +6586,14 @@
       <c r="D208" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="209" spans="1:4">
+      <c r="E208" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F208" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
       <c r="A209" s="2" t="s">
         <v>666</v>
       </c>
@@ -5326,8 +6606,14 @@
       <c r="D209" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="210" spans="1:4">
+      <c r="E209" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F209" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
       <c r="A210" s="2" t="s">
         <v>667</v>
       </c>
@@ -5340,8 +6626,14 @@
       <c r="D210" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="211" spans="1:4">
+      <c r="E210" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F210" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
       <c r="A211" s="2" t="s">
         <v>668</v>
       </c>
@@ -5354,8 +6646,14 @@
       <c r="D211" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="212" spans="1:4">
+      <c r="E211" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F211" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
       <c r="A212" s="2" t="s">
         <v>669</v>
       </c>
@@ -5368,8 +6666,14 @@
       <c r="D212" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="213" spans="1:4">
+      <c r="E212" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F212" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
       <c r="A213" s="2" t="s">
         <v>670</v>
       </c>
@@ -5382,8 +6686,14 @@
       <c r="D213" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="214" spans="1:4">
+      <c r="E213" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F213" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
       <c r="A214" s="2" t="s">
         <v>671</v>
       </c>
@@ -5396,8 +6706,14 @@
       <c r="D214" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="215" spans="1:4">
+      <c r="E214" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F214" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
       <c r="A215" s="2" t="s">
         <v>672</v>
       </c>
@@ -5410,8 +6726,14 @@
       <c r="D215" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="216" spans="1:4">
+      <c r="E215" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F215" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
       <c r="A216" s="2" t="s">
         <v>673</v>
       </c>
@@ -5424,8 +6746,14 @@
       <c r="D216" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="217" spans="1:4">
+      <c r="E216" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F216" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
       <c r="A217" s="2" t="s">
         <v>674</v>
       </c>
@@ -5438,8 +6766,14 @@
       <c r="D217" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="218" spans="1:4">
+      <c r="E217" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F217" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
       <c r="A218" s="2" t="s">
         <v>675</v>
       </c>
@@ -5452,8 +6786,14 @@
       <c r="D218" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="219" spans="1:4">
+      <c r="E218" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F218" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
       <c r="A219" s="2" t="s">
         <v>676</v>
       </c>
@@ -5466,24 +6806,34 @@
       <c r="D219" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="220" spans="1:4">
+      <c r="E219" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F219" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
-    </row>
-    <row r="221" spans="1:4">
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+    </row>
+    <row r="221" spans="1:6">
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
-    </row>
-    <row r="222" spans="1:4">
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+    </row>
+    <row r="222" spans="1:6">
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
     </row>
-    <row r="223" spans="1:4">
+    <row r="223" spans="1:6">
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
     </row>
-    <row r="224" spans="1:4">
+    <row r="224" spans="1:6">
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
     </row>
@@ -8318,6 +9668,43 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <WS_KM xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">false</WS_KM>
+    <Language xmlns="49800bc8-27f6-4a38-98b2-e471baa92d6a" xsi:nil="true"/>
+    <TaxCatchAll xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7" xsi:nil="true"/>
+    <TaxKeywordTaxHTField xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </TaxKeywordTaxHTField>
+    <i51f003d86e044fa8787db0c1fd77971 xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </i51f003d86e044fa8787db0c1fd77971>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="49800bc8-27f6-4a38-98b2-e471baa92d6a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_Flow_SignoffStatus xmlns="49800bc8-27f6-4a38-98b2-e471baa92d6a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"excel-template-wavestone","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+</file>
+
+<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Groups X - Document" ma:contentTypeID="0x0101002FECBCFE27A94FA4A49D56DA0627A7A700D5CF0826E9A3234B8339779C1FAEB6D1" ma:contentTypeVersion="26" ma:contentTypeDescription="Content type used in default document library in Groups for external groups (no extra fields for metadata provided)" ma:contentTypeScope="" ma:versionID="279e6f4b32e9b65a6d75abd62779577b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="0e0560a2-5f28-40fd-a47f-413e3deae4f7" xmlns:ns3="49800bc8-27f6-4a38-98b2-e471baa92d6a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="16811575601f31dfff62ec4a7f080727" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -8629,44 +10016,45 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyTemplateConfiguration><![CDATA[{"transformationConfigurations":[],"templateName":"excel-template-wavestone","templateDescription":"","enableDocumentContentUpdater":false,"version":"2.0"}]]></TemplafyTemplateConfiguration>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60AEAD36-3C40-43A4-8069-DD963241733E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<TemplafyFormConfiguration><![CDATA[{"formFields":[],"formDataEntries":[]}]]></TemplafyFormConfiguration>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD40D982-8286-4B8F-A856-9520176C5B63}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="0e0560a2-5f28-40fd-a47f-413e3deae4f7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="49800bc8-27f6-4a38-98b2-e471baa92d6a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <WS_KM xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">false</WS_KM>
-    <Language xmlns="49800bc8-27f6-4a38-98b2-e471baa92d6a" xsi:nil="true"/>
-    <TaxCatchAll xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7" xsi:nil="true"/>
-    <TaxKeywordTaxHTField xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </TaxKeywordTaxHTField>
-    <i51f003d86e044fa8787db0c1fd77971 xmlns="0e0560a2-5f28-40fd-a47f-413e3deae4f7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </i51f003d86e044fa8787db0c1fd77971>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="49800bc8-27f6-4a38-98b2-e471baa92d6a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_Flow_SignoffStatus xmlns="49800bc8-27f6-4a38-98b2-e471baa92d6a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0BA3DF0-87BD-4820-849B-A09A7499F975}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item5.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6833886D-AFD0-4394-A643-4CABE4FE0F96}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F97C02F-FADE-4CE7-BA0C-A8E70A521F21}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8684,42 +10072,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6833886D-AFD0-4394-A643-4CABE4FE0F96}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0BA3DF0-87BD-4820-849B-A09A7499F975}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD40D982-8286-4B8F-A856-9520176C5B63}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="0e0560a2-5f28-40fd-a47f-413e3deae4f7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="49800bc8-27f6-4a38-98b2-e471baa92d6a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps5.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60AEAD36-3C40-43A4-8069-DD963241733E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/Framework_1_Belgique.xlsx
+++ b/data/Framework_1_Belgique.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://digiplace-my.sharepoint.com/personal/aurelien_brun_wavestone_com/Documents/Desktop/mapper/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="258" documentId="8_{6DCC9DED-70CC-49C8-8D15-2391C499D3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B36ECE3-3F66-4F07-9468-2FA889A36BC3}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="8_{6DCC9DED-70CC-49C8-8D15-2391C499D3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D3F8920-4C90-426C-A46A-8AF0D76F4FBD}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4850" yWindow="4510" windowWidth="5610" windowHeight="3200" xr2:uid="{B5DE09A6-CED4-42BE-9EC0-2641ED5338CA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{B5DE09A6-CED4-42BE-9EC0-2641ED5338CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Belgique Cyfun 2025" sheetId="2" r:id="rId1"/>
@@ -6746,10 +6746,10 @@
       <c r="D216" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E216" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F216" s="2" t="b">
+      <c r="E216" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F216" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6766,10 +6766,10 @@
       <c r="D217" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E217" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F217" s="2" t="b">
+      <c r="E217" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F217" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6786,10 +6786,10 @@
       <c r="D218" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E218" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F218" s="2" t="b">
+      <c r="E218" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F218" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6806,10 +6806,10 @@
       <c r="D219" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E219" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F219" s="2" t="b">
+      <c r="E219" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F219" s="4" t="b">
         <v>1</v>
       </c>
     </row>
